--- a/outputs/Склад с товаром в пути.xlsx
+++ b/outputs/Склад с товаром в пути.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -550,11 +550,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
+          <t>VT Reedle Shot</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42</v>
+        <v>452</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>42</v>
+        <v>452</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="2" t="n">
-        <v>42</v>
+        <v>452</v>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -582,29 +582,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dm7dm3</t>
+          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>100</v>
+        <v>448</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>194988</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -614,11 +616,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dm7dm5</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g]</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>100</v>
+        <v>529</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
@@ -627,14 +629,14 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>100</v>
+        <v>529</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="2" t="n">
-        <v>100</v>
+        <v>529</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -646,11 +648,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dm7dm6</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
@@ -659,14 +661,14 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -678,29 +680,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dm7dm9</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>100</v>
+        <v>956</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>956</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>801357</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -710,29 +714,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dm7dm10</t>
+          <t>manyo_bifida_biome_toner</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>1200</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>565812</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -742,29 +748,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dm7dm12</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>264616</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -772,597 +780,629 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>dm7dm11</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>264616</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>646</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>646</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>556</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>СГ-Белая</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>831</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>831</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>621</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>СГ-Красная</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1439</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1439</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1094</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>manyo_bifida_biome_toner</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>565812</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1376</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1376</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1121</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>956</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="n">
-        <v>956</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>801357</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>VT PDRN Essence 100</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1063</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1033</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dm7dm1</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>9707</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>9707</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>9347</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g]</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>428</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>428</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dm7dm11-65</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Round Lab 1025 Dokdo Toner</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>990</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1245</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>760129</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>VT Reedle Shot</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>dm7dm5-50</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>dm7dm5-45</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>492</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>477</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>292191</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dm7dm3-50</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA_galactomyces_Ample</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dm7dm3-45</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>dm7dm11-50</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1297</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>832</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 32.8 мес</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>dm7dm11-45</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1483</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1483</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>943</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 32.2 мес</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>194988</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Enoughcollagenwhiteningcovertip03</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>781</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>781</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>496</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 32.1 мес</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Триммер Золото</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Etude Baking Powder Crunch Pore Scrub</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>7310</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>7310</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>4325</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 29.1 мес</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>JIGOTT - MASK 15</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -1371,32 +1411,32 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>36</v>
+        <v>28.6</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1094</v>
+        <v>845</v>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 28.6 мес</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>420</v>
+        <v>1611</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0</v>
@@ -1405,32 +1445,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>420</v>
+        <v>1611</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>345</v>
+        <v>891</v>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 27.0 мес</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1376</v>
+        <v>67</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0</v>
@@ -1439,32 +1479,32 @@
         <v>0</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1376</v>
+        <v>67</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1121</v>
+        <v>37</v>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 27.0 мес</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>646</v>
+        <v>159</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0</v>
@@ -1473,68 +1513,66 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>646</v>
+        <v>159</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>36</v>
+        <v>25.8</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>556</v>
+        <v>84</v>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 25.8 мес</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Round Lab 1025 Dokdo Toner</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>990</v>
+        <v>3489</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1350</v>
+        <v>3489</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>36</v>
+        <v>23.1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1245</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>760129</v>
-      </c>
+        <v>1689</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 23.1 мес</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
+          <t>Petitfee Pink Vita Brightening Eye Mask</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>831</v>
+        <v>200</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0</v>
@@ -1543,32 +1581,32 @@
         <v>0</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>831</v>
+        <v>200</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>36</v>
+        <v>22.6</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>621</v>
+        <v>95</v>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 22.6 мес</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>VT PDRN Essence 100</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>1063</v>
+        <v>7429</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0</v>
@@ -1577,32 +1615,32 @@
         <v>0</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1063</v>
+        <v>7429</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>36</v>
+        <v>21.1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1033</v>
+        <v>3319</v>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 21.1 мес</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+          <t>HairSet/350/8*2</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0</v>
@@ -1611,32 +1649,32 @@
         <v>0</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>36</v>
+        <v>20.8</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 20.8 мес</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>0</v>
@@ -1645,32 +1683,32 @@
         <v>0</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>36</v>
+        <v>19.2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>398</v>
+        <v>163</v>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 19.2 мес</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>96</v>
+        <v>375</v>
       </c>
       <c r="C37" s="4" t="n">
         <v>0</v>
@@ -1679,66 +1717,68 @@
         <v>0</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>96</v>
+        <v>375</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 19.0 мес</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ELIZAVECCA_galactomyces_Ample</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>137</v>
+        <v>7302</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>25020</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>137</v>
+        <v>32322</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
+        <v>1369</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>36</v>
+        <v>18.1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="I38" s="4" t="inlineStr"/>
+        <v>11787</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>5909200</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 18.1 мес</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
+          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>0</v>
@@ -1747,32 +1787,32 @@
         <v>0</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>36</v>
+        <v>17.9</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 17.9 мес</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]</t>
+          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>9707</v>
+        <v>642</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>0</v>
@@ -1781,68 +1821,68 @@
         <v>0</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>9707</v>
+        <v>642</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>36</v>
+        <v>17.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>9347</v>
+        <v>207</v>
       </c>
       <c r="I40" s="4" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 17.3 мес</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]</t>
+          <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>12</v>
+        <v>4492</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>480</v>
+        <v>25008</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>492</v>
+        <v>44500</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>2027</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>36</v>
+        <v>17.2</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>477</v>
+        <v>14095</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>292191</v>
+        <v>10144989</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 17.2 мес</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>1297</v>
+        <v>352</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
@@ -1851,32 +1891,32 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1297</v>
+        <v>352</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>32.8</v>
+        <v>17.2</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>832</v>
+        <v>112</v>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.8 мес</t>
+          <t>излишек: хватит на 17.2 мес</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+          <t>Petitfee GOLD</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>1483</v>
+        <v>416</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>0</v>
@@ -1885,32 +1925,32 @@
         <v>0</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1483</v>
+        <v>416</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>32.2</v>
+        <v>15.7</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>943</v>
+        <v>101</v>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.2 мес</t>
+          <t>излишек: хватит на 15.7 мес</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip03</t>
+          <t>Manyo_Complex_Ampoule</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>781</v>
+        <v>1351</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>0</v>
@@ -1919,32 +1959,32 @@
         <v>0</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>781</v>
+        <v>1351</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>32.1</v>
+        <v>15.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>496</v>
+        <v>331</v>
       </c>
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.1 мес</t>
+          <t>излишек: хватит на 15.7 мес</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>7310</v>
+        <v>1500</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>0</v>
@@ -1953,32 +1993,32 @@
         <v>0</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>7310</v>
+        <v>1500</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>29.1</v>
+        <v>15.5</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>4325</v>
+        <v>345</v>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 29.1 мес</t>
+          <t>излишек: хватит на 15.5 мес</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - MASK 15</t>
+          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>1445</v>
+        <v>187</v>
       </c>
       <c r="C46" s="4" t="n">
         <v>0</v>
@@ -1987,32 +2027,32 @@
         <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1445</v>
+        <v>187</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>28.6</v>
+        <v>15.1</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>845</v>
+        <v>37</v>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 28.6 мес</t>
+          <t>излишек: хватит на 15.1 мес</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>67</v>
+        <v>360</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>0</v>
@@ -2021,32 +2061,32 @@
         <v>0</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>67</v>
+        <v>360</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>27</v>
+        <v>14.7</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 27.0 мес</t>
+          <t>излишек: хватит на 14.7 мес</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>1611</v>
+        <v>117</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>0</v>
@@ -2055,32 +2095,32 @@
         <v>0</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1611</v>
+        <v>117</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>27</v>
+        <v>13.7</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>891</v>
+        <v>12</v>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 27.0 мес</t>
+          <t>излишек: хватит на 13.7 мес</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
+          <t>PETITFEE MASK 5</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>0</v>
@@ -2089,32 +2129,32 @@
         <v>0</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>25.8</v>
+        <v>13.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 25.8 мес</t>
+          <t>излишек: хватит на 13.7 мес</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
+          <t>Enoughcollagenwhiteningcovertip</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>3489</v>
+        <v>663</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>0</v>
@@ -2123,32 +2163,32 @@
         <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3489</v>
+        <v>663</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>23.1</v>
+        <v>13.2</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1689</v>
+        <v>48</v>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 23.1 мес</t>
+          <t>излишек: хватит на 13.2 мес</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Petitfee Pink Vita Brightening Eye Mask</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>200</v>
+        <v>648</v>
       </c>
       <c r="C51" s="4" t="n">
         <v>0</v>
@@ -2157,32 +2197,32 @@
         <v>0</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>200</v>
+        <v>648</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>22.6</v>
+        <v>12.8</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 22.6 мес</t>
+          <t>излишек: хватит на 12.8 мес</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>7429</v>
+        <v>1490</v>
       </c>
       <c r="C52" s="4" t="n">
         <v>0</v>
@@ -2191,32 +2231,32 @@
         <v>0</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>7429</v>
+        <v>1490</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>274</v>
+        <v>96</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>21.1</v>
+        <v>12.5</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>3319</v>
+        <v>50</v>
       </c>
       <c r="I52" s="4" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 21.1 мес</t>
+          <t>излишек: хватит на 12.5 мес</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>HairSet/350/8*2</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>107</v>
+        <v>989</v>
       </c>
       <c r="C53" s="4" t="n">
         <v>0</v>
@@ -2225,648 +2265,646 @@
         <v>0</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>107</v>
+        <v>989</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>20.8</v>
+        <v>12.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 20.8 мес</t>
+          <t>излишек: хватит на 12.2 мес</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>403</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>403</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 19.2 мес</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COSRX_Salicylic_Acid_Cleanser</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G54" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>375</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>375</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 19.0 мес</t>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - CER-100  [100ml]</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G55" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>7302</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>25020</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>32322</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>1369</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>11787</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>5909200</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 18.1 мес</t>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Black</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>420</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>420</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 17.9 мес</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2424</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>2424</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="G57" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>642</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>642</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 17.3 мес</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Disney</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G58" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 17.2 мес</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Celimax Dual Barrier Creamy Toner</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>4492</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>25008</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>44500</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>14095</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>10144989</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 17.2 мес</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Manyo_Complex_Ampoule</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>1351</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>1351</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>331</v>
-      </c>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 15.7 мес</t>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>6238</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>6238</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Petitfee GOLD</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml]</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Manyo_Galac_Vita_Serum</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>521</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>521</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G65" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 21</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>3348</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>3348</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G68" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>7304</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>7304</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="G69" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
         <v>416</v>
       </c>
-      <c r="C62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4" t="n">
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="n">
         <v>416</v>
       </c>
-      <c r="F62" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 15.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>345</v>
-      </c>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 15.5 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>187</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>187</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 15.1 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 14.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 13.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>PETITFEE MASK 5</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 13.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Enoughcollagenwhiteningcovertip</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>663</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>663</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 13.2 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.8 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.5 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.2 мес</t>
+      <c r="F71" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G71" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COSRX_Salicylic_Acid_Cleanser</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>358</v>
+        <v>893</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0</v>
@@ -2875,13 +2913,13 @@
         <v>0</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>358</v>
+        <v>893</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="G72" t="n">
-        <v>11.3</v>
+        <v>6.7</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -2896,11 +2934,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100  [100ml]</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>464</v>
+        <v>922</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0</v>
@@ -2909,13 +2947,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>464</v>
+        <v>922</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
@@ -2930,31 +2968,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black</t>
+          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1030</v>
+        <v>200</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="G74" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -2964,11 +3004,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>2424</v>
+        <v>3120</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0</v>
@@ -2977,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>2424</v>
+        <v>3120</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>182</v>
+        <v>342</v>
       </c>
       <c r="G75" t="n">
-        <v>10.3</v>
+        <v>6.4</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>0</v>
@@ -2998,11 +3038,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Disney</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>836</v>
+        <v>395</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0</v>
@@ -3011,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>836</v>
+        <v>395</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G76" t="n">
-        <v>10.1</v>
+        <v>6.2</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>0</v>
@@ -3032,11 +3072,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>278</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0</v>
@@ -3045,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>278</v>
+        <v>484</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G77" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
@@ -3066,11 +3106,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER</t>
+          <t>Manyo_Ampoule_Lotion</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46</v>
+        <v>615</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0</v>
@@ -3079,13 +3119,13 @@
         <v>0</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46</v>
+        <v>615</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="G78" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
@@ -3100,11 +3140,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
+          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6238</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0</v>
@@ -3113,13 +3153,13 @@
         <v>0</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>6238</v>
+        <v>13</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>563</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>0</v>
@@ -3134,11 +3174,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0</v>
@@ -3147,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G80" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
@@ -3168,11 +3208,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml]</t>
+          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>53</v>
+        <v>582</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>0</v>
@@ -3181,13 +3221,13 @@
         <v>0</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>53</v>
+        <v>582</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G81" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>0</v>
@@ -3202,11 +3242,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>Manyo_Pure_Cleansing_Oil</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>521</v>
+        <v>194</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>0</v>
@@ -3215,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>521</v>
+        <v>194</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G82" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>0</v>
@@ -3236,31 +3276,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Manyo_Galac_Vita_Serum</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>753</v>
+        <v>93</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>753</v>
+        <v>793</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="G83" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3270,11 +3312,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 21</t>
+          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>251</v>
+        <v>318</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>0</v>
@@ -3283,13 +3325,13 @@
         <v>0</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>251</v>
+        <v>318</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G84" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
@@ -3304,11 +3346,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>7304</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>0</v>
@@ -3317,13 +3359,13 @@
         <v>0</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>7304</v>
+        <v>289</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>709</v>
+        <v>52</v>
       </c>
       <c r="G85" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>0</v>
@@ -3338,33 +3380,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>400</v>
+        <v>931</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="G86" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3374,11 +3414,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>3348</v>
+        <v>722</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>0</v>
@@ -3387,13 +3427,13 @@
         <v>0</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>3348</v>
+        <v>722</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="G87" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>0</v>
@@ -3408,11 +3448,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>0</v>
@@ -3421,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G88" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>0</v>
@@ -3442,11 +3482,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>416</v>
+        <v>320</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>0</v>
@@ -3455,13 +3495,13 @@
         <v>0</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>416</v>
+        <v>320</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G89" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>0</v>
@@ -3476,11 +3516,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>PETITFEE MASK 6</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>893</v>
+        <v>106</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>0</v>
@@ -3489,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>893</v>
+        <v>106</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="G90" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
@@ -3510,11 +3550,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+          <t>videokamera4gneww</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>922</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>0</v>
@@ -3523,13 +3563,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>922</v>
+        <v>5</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>0</v>
@@ -3544,33 +3584,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G92" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3580,31 +3618,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>3120</v>
+        <v>61</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>3120</v>
+        <v>461</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>342</v>
+        <v>95</v>
       </c>
       <c r="G93" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3614,11 +3654,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>395</v>
+        <v>552</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>0</v>
@@ -3627,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>395</v>
+        <v>552</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="G94" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>0</v>
@@ -3648,11 +3688,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
+          <t>Enoughcollagenwhiteningcovertip01</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>0</v>
@@ -3661,13 +3701,13 @@
         <v>0</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="G95" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>0</v>
@@ -3682,11 +3722,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Manyo_Ampoule_Lotion</t>
+          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>615</v>
+        <v>345</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>0</v>
@@ -3695,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>615</v>
+        <v>345</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G96" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>0</v>
@@ -3716,11 +3756,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
+          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>0</v>
@@ -3729,13 +3769,13 @@
         <v>0</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="G97" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>0</v>
@@ -3750,11 +3790,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>0</v>
@@ -3763,13 +3803,13 @@
         <v>0</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="G98" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>0</v>
@@ -3784,11 +3824,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>582</v>
+        <v>909</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>0</v>
@@ -3797,13 +3837,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>582</v>
+        <v>909</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="G99" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>0</v>
@@ -3818,11 +3858,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Manyo_Pure_Cleansing_Oil</t>
+          <t>Petitfee EGF</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>0</v>
@@ -3831,13 +3871,13 @@
         <v>0</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G100" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>0</v>
@@ -3852,33 +3892,31 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>793</v>
+        <v>30</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="G101" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3888,11 +3926,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
+          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>318</v>
+        <v>9</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>0</v>
@@ -3901,13 +3939,13 @@
         <v>0</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>318</v>
+        <v>9</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>0</v>
@@ -3922,11 +3960,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>931</v>
+        <v>153</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>0</v>
@@ -3935,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>931</v>
+        <v>153</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="G103" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
@@ -3956,11 +3994,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>289</v>
+        <v>50</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>0</v>
@@ -3969,13 +4007,13 @@
         <v>0</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>289</v>
+        <v>50</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="G104" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>0</v>
@@ -3990,11 +4028,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>722</v>
+        <v>31</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>0</v>
@@ -4003,13 +4041,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>722</v>
+        <v>31</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="G105" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>0</v>
@@ -4024,11 +4062,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
+          <t>JIGOTT - Collagen Healing Cream [100ml]</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>0</v>
@@ -4037,13 +4075,13 @@
         <v>0</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G106" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>0</v>
@@ -4058,11 +4096,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PETITFEE MASK 6</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C107" s="2" t="n">
         <v>0</v>
@@ -4071,13 +4109,13 @@
         <v>0</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="G107" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>0</v>
@@ -4092,11 +4130,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>videokamera4gneww</t>
+          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pearl [1/2/3]*[10ea]</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C108" s="2" t="n">
         <v>0</v>
@@ -4105,13 +4143,13 @@
         <v>0</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>0</v>
@@ -4126,11 +4164,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
+          <t>EKEL Ampule Сream Сollagen [70ml]</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>320</v>
+        <v>71</v>
       </c>
       <c r="C109" s="2" t="n">
         <v>0</v>
@@ -4139,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>320</v>
+        <v>71</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="G109" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>0</v>
@@ -4160,11 +4198,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
+          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatment [50ml]</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C110" s="2" t="n">
         <v>0</v>
@@ -4173,13 +4211,13 @@
         <v>0</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
@@ -4194,33 +4232,31 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
+          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="C111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>461</v>
+        <v>162</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="G111" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -4230,11 +4266,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
+          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>552</v>
+        <v>4</v>
       </c>
       <c r="C112" s="2" t="n">
         <v>0</v>
@@ -4243,13 +4279,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>552</v>
+        <v>4</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>0</v>
@@ -4264,11 +4300,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip01</t>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>463</v>
+        <v>12</v>
       </c>
       <c r="C113" s="2" t="n">
         <v>0</v>
@@ -4277,13 +4313,13 @@
         <v>0</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>463</v>
+        <v>12</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="G113" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>0</v>
@@ -4298,11 +4334,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
+          <t>Collagen_Enough_Moisture_Foundation_21</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="C114" s="2" t="n">
         <v>0</v>
@@ -4311,13 +4347,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="G114" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>0</v>
@@ -4332,11 +4368,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
+          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml]</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>147</v>
+        <v>5</v>
       </c>
       <c r="C115" s="2" t="n">
         <v>0</v>
@@ -4345,13 +4381,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>147</v>
+        <v>5</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>0</v>
@@ -4366,11 +4402,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
+          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>252</v>
+        <v>17</v>
       </c>
       <c r="C116" s="2" t="n">
         <v>0</v>
@@ -4379,13 +4415,13 @@
         <v>0</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>252</v>
+        <v>17</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G116" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>0</v>
@@ -4400,11 +4436,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
+          <t>I'm Sorry for My Skin Крем Age Capture Vitalizer</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>909</v>
+        <v>10</v>
       </c>
       <c r="C117" s="2" t="n">
         <v>0</v>
@@ -4413,13 +4449,13 @@
         <v>0</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>909</v>
+        <v>10</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>269</v>
+        <v>14</v>
       </c>
       <c r="G117" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>0</v>
@@ -4434,11 +4470,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Petitfee EGF</t>
+          <t>Collagen_Enough_Moisture_Foundation_13</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="C118" s="2" t="n">
         <v>0</v>
@@ -4447,13 +4483,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="G118" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>0</v>
@@ -4468,11 +4504,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C119" s="2" t="n">
         <v>0</v>
@@ -4481,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G119" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>0</v>
@@ -4502,11 +4538,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hydrogel Eye Patch</t>
+          <t>Etude Baking Powder Crunch Pore Scrub треугольники 30</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C120" s="2" t="n">
         <v>0</v>
@@ -4515,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G120" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>0</v>
@@ -4536,11 +4572,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
+          <t>Dr.Jart_Teatreatment_Toner</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="C121" s="2" t="n">
         <v>0</v>
@@ -4549,13 +4585,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G121" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>0</v>
@@ -4570,11 +4606,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C122" s="2" t="n">
         <v>0</v>
@@ -4583,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>0</v>
@@ -4604,11 +4640,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 13</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C123" s="2" t="n">
         <v>0</v>
@@ -4617,13 +4653,13 @@
         <v>0</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="G123" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>0</v>
@@ -4638,11 +4674,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Healing Cream [100ml]</t>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C124" s="2" t="n">
         <v>0</v>
@@ -4651,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>0</v>
@@ -4672,11 +4708,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
+          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="C125" s="2" t="n">
         <v>0</v>
@@ -4685,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="G125" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>0</v>
@@ -4706,11 +4742,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pearl [1/2/3]*[10ea]</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C126" s="2" t="n">
         <v>0</v>
@@ -4719,13 +4755,13 @@
         <v>0</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G126" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>0</v>
@@ -4740,11 +4776,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EKEL Ampule Сream Сollagen [70ml]</t>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="C127" s="2" t="n">
         <v>0</v>
@@ -4753,13 +4789,13 @@
         <v>0</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G127" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>0</v>
@@ -4772,748 +4808,34 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Рация_UV-82 (1 шт)</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Скалер белый v1</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatment [50ml]</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="G132" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Collagen_Enough_Moisture_Foundation_21</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Пистолет перкуссионный V1</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>I'm Sorry for My Skin Крем Age Capture Vitalizer</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml]</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Collagen_Enough_Moisture_Foundation_13</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Etude Baking Powder Crunch Pore Scrub треугольники 30</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="G142" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Dr.Jart_Teatreatment_Toner</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 13</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B149" s="6" t="n">
-        <v>106304</v>
-      </c>
-      <c r="C149" s="6" t="n">
+      <c r="B128" s="6" t="n">
+        <v>104629</v>
+      </c>
+      <c r="C128" s="6" t="n">
         <v>54916</v>
       </c>
-      <c r="D149" s="6" t="n">
+      <c r="D128" s="6" t="n">
         <v>17700</v>
       </c>
-      <c r="E149" s="6" t="n">
-        <v>178920</v>
-      </c>
-      <c r="F149" s="6" t="n">
-        <v>10974</v>
-      </c>
-      <c r="G149" s="5" t="inlineStr"/>
-      <c r="H149" s="6" t="n">
-        <v>65711</v>
-      </c>
-      <c r="I149" s="6" t="n">
+      <c r="E128" s="6" t="n">
+        <v>177245</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>10956</v>
+      </c>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="6" t="n">
+        <v>64061</v>
+      </c>
+      <c r="I128" s="6" t="n">
         <v>19912572</v>
       </c>
-      <c r="J149" s="5" t="inlineStr"/>
+      <c r="J128" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5526,7 +4848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -6484,11 +5806,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>420</v>
+        <v>1500</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -6497,13 +5819,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>420</v>
+        <v>1500</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>345</v>
@@ -6511,18 +5833,18 @@
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 15.5 мес</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1500</v>
+        <v>420</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0</v>
@@ -6531,13 +5853,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1500</v>
+        <v>420</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>345</v>
@@ -6545,7 +5867,7 @@
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.5 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
@@ -6856,269 +6178,285 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dm7dm12</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Petitfee Pink Vita Brightening Eye Mask</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 22.6 мес</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>dm7dm5-50</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 25.8 мес</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dm7dm3-50</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dm7dm11-50</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>СГ-Белая</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 14.7 мес</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>dm7dm6</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 12.5 мес</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>dm7dm11</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Enoughcollagenwhiteningcovertip</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>663</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>663</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 13.2 мес</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dm7dm11-45</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>HairSet/350/8*2</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 20.8 мес</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>СГ-Красная</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0</v>
@@ -7127,14 +6465,14 @@
         <v>0</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" t="inlineStr">
@@ -7144,798 +6482,206 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>dm7dm5-45</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 15.1 мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 27.0 мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 12.8 мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>989</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>989</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 12.2 мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 13.7 мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>PETITFEE MASK 5</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="n">
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dm7dm3-45</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>dm7dm5</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>dm7dm9</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>dm7dm10</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>dm7dm3</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>dm7dm1</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Petitfee Pink Vita Brightening Eye Mask</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 22.6 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>159</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>159</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 25.8 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 36 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 36 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 14.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.5 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>dm7dm11-65</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Enoughcollagenwhiteningcovertip</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>663</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>663</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 13.2 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>HairSet/350/8*2</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 20.8 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 27.0 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>187</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>187</v>
-      </c>
-      <c r="F66" s="4" t="n">
+      <c r="F53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 15.1 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.8 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.2 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 13.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>PETITFEE MASK 5</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 13.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Триммер Золото</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
         </is>
       </c>
     </row>

--- a/outputs/Склад с товаром в пути.xlsx
+++ b/outputs/Склад с товаром в пути.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -516,31 +516,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule Foam [125ml]</t>
+          <t>VT Reedle Shot</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1500</v>
+        <v>452</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>979290</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -550,29 +548,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VT Reedle Shot</t>
+          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>194988</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -582,31 +582,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g]</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>194988</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -616,11 +614,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g]</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>529</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
@@ -629,14 +627,14 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>529</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="2" t="n">
-        <v>529</v>
+        <v>42</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -648,11 +646,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
@@ -661,14 +659,14 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="2" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -678,115 +676,117 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>956</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" s="2" t="n">
-        <v>956</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>801357</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>manyo_bifida_biome_toner</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>565812</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>646</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>646</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>556</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>264616</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Round Lab 1025 Dokdo Toner</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>990</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1245</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>760129</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>152</v>
+        <v>831</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0</v>
@@ -795,16 +795,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>152</v>
+        <v>831</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>122</v>
+        <v>621</v>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
@@ -816,11 +816,11 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+          <t>VT PDRN Essence 100</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>646</v>
+        <v>1063</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0</v>
@@ -829,16 +829,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>646</v>
+        <v>1063</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>556</v>
+        <v>1033</v>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
@@ -850,11 +850,11 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>831</v>
+        <v>428</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0</v>
@@ -863,16 +863,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>831</v>
+        <v>428</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>621</v>
+        <v>398</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
@@ -884,11 +884,11 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1439</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0</v>
@@ -897,16 +897,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1439</v>
+        <v>96</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1094</v>
+        <v>81</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
@@ -918,11 +918,11 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1376</v>
+        <v>420</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0</v>
@@ -931,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1376</v>
+        <v>420</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1121</v>
+        <v>345</v>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>VT PDRN Essence 100</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1063</v>
+        <v>1376</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0</v>
@@ -965,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1063</v>
+        <v>1376</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1033</v>
+        <v>1121</v>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
@@ -986,31 +986,33 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]</t>
+          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9707</v>
+        <v>12</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9707</v>
+        <v>492</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>9347</v>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
+        <v>477</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>292191</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 36 мес</t>
@@ -1020,11 +1022,11 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
+          <t>ELIZAVECCA_galactomyces_Ample</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>428</v>
+        <v>137</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0</v>
@@ -1033,16 +1035,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>428</v>
+        <v>137</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>398</v>
+        <v>122</v>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
@@ -1054,33 +1056,31 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Round Lab 1025 Dokdo Toner</t>
+          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>990</v>
+        <v>79</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1350</v>
+        <v>79</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1245</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>760129</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 36 мес</t>
@@ -1090,11 +1090,11 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>420</v>
+        <v>1439</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0</v>
@@ -1103,16 +1103,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>420</v>
+        <v>1439</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>345</v>
+        <v>1094</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr">
@@ -1124,11 +1124,11 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>96</v>
+        <v>9707</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>96</v>
+        <v>9707</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>81</v>
+        <v>9347</v>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr">
@@ -1158,47 +1158,45 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>12</v>
+        <v>1297</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>492</v>
+        <v>1297</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>36</v>
+        <v>32.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>477</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>292191</v>
-      </c>
+        <v>832</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 32.8 мес</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ELIZAVECCA_galactomyces_Ample</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>137</v>
+        <v>1483</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0</v>
@@ -1207,32 +1205,32 @@
         <v>0</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>137</v>
+        <v>1483</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>36</v>
+        <v>32.2</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>122</v>
+        <v>943</v>
       </c>
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 32.2 мес</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
+          <t>Enoughcollagenwhiteningcovertip03</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>79</v>
+        <v>781</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0</v>
@@ -1241,32 +1239,32 @@
         <v>0</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>79</v>
+        <v>781</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36</v>
+        <v>32.1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>64</v>
+        <v>496</v>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 32.1 мес</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]</t>
+          <t>Etude Baking Powder Crunch Pore Scrub</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1297</v>
+        <v>7310</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
@@ -1275,32 +1273,32 @@
         <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1297</v>
+        <v>7310</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>832</v>
+        <v>4325</v>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.8 мес</t>
+          <t>излишек: хватит на 29.1 мес</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+          <t>JIGOTT - MASK 15</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1483</v>
+        <v>1445</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0</v>
@@ -1309,32 +1307,32 @@
         <v>0</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1483</v>
+        <v>1445</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>32.2</v>
+        <v>28.6</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>943</v>
+        <v>845</v>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.2 мес</t>
+          <t>излишек: хватит на 28.6 мес</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip03</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>781</v>
+        <v>1611</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0</v>
@@ -1343,32 +1341,32 @@
         <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>781</v>
+        <v>1611</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>32.1</v>
+        <v>27</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>496</v>
+        <v>891</v>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.1 мес</t>
+          <t>излишек: хватит на 27.0 мес</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>7310</v>
+        <v>67</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
@@ -1377,32 +1375,32 @@
         <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7310</v>
+        <v>67</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>29.1</v>
+        <v>27</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4325</v>
+        <v>37</v>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 29.1 мес</t>
+          <t>излишек: хватит на 27.0 мес</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - MASK 15</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1445</v>
+        <v>159</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -1411,32 +1409,32 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1445</v>
+        <v>159</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>28.6</v>
+        <v>25.8</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>845</v>
+        <v>84</v>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 28.6 мес</t>
+          <t>излишек: хватит на 25.8 мес</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1611</v>
+        <v>3489</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0</v>
@@ -1445,32 +1443,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1611</v>
+        <v>3489</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>27</v>
+        <v>23.1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>891</v>
+        <v>1689</v>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 27.0 мес</t>
+          <t>излишек: хватит на 23.1 мес</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+          <t>Petitfee Pink Vita Brightening Eye Mask</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0</v>
@@ -1479,32 +1477,32 @@
         <v>0</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>27</v>
+        <v>22.6</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 27.0 мес</t>
+          <t>излишек: хватит на 22.6 мес</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>159</v>
+        <v>7429</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0</v>
@@ -1513,32 +1511,32 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>159</v>
+        <v>7429</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5</v>
+        <v>274</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>25.8</v>
+        <v>21.1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>84</v>
+        <v>3319</v>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 25.8 мес</t>
+          <t>излишек: хватит на 21.1 мес</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
+          <t>HairSet/350/8*2</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>3489</v>
+        <v>107</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0</v>
@@ -1547,32 +1545,32 @@
         <v>0</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3489</v>
+        <v>107</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>23.1</v>
+        <v>20.8</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1689</v>
+        <v>47</v>
       </c>
       <c r="I32" s="4" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 23.1 мес</t>
+          <t>излишек: хватит на 20.8 мес</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Petitfee Pink Vita Brightening Eye Mask</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0</v>
@@ -1581,32 +1579,32 @@
         <v>0</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>22.6</v>
+        <v>19.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 22.6 мес</t>
+          <t>излишек: хватит на 19.2 мес</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>7429</v>
+        <v>375</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0</v>
@@ -1615,66 +1613,68 @@
         <v>0</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7429</v>
+        <v>375</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>274</v>
+        <v>15</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>21.1</v>
+        <v>19</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3319</v>
+        <v>150</v>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 21.1 мес</t>
+          <t>излишек: хватит на 19.0 мес</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HairSet/350/8*2</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>107</v>
+        <v>7302</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0</v>
+        <v>25020</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>107</v>
+        <v>32322</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4</v>
+        <v>1369</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="I35" s="4" t="inlineStr"/>
+        <v>11787</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>5909200</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 20.8 мес</t>
+          <t>излишек: хватит на 18.1 мес</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
+          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>0</v>
@@ -1683,32 +1683,32 @@
         <v>0</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>19.2</v>
+        <v>17.9</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 19.2 мес</t>
+          <t>излишек: хватит на 17.9 мес</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
+          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>375</v>
+        <v>642</v>
       </c>
       <c r="C37" s="4" t="n">
         <v>0</v>
@@ -1717,102 +1717,102 @@
         <v>0</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>375</v>
+        <v>642</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 19.0 мес</t>
+          <t>излишек: хватит на 17.3 мес</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>7302</v>
+        <v>352</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>25020</v>
+        <v>0</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>32322</v>
+        <v>352</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1369</v>
+        <v>16</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>18.1</v>
+        <v>17.2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>11787</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>5909200</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 18.1 мес</t>
+          <t>излишек: хватит на 17.2 мес</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
+          <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>420</v>
+        <v>4492</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0</v>
+        <v>25008</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>420</v>
+        <v>44500</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>18</v>
+        <v>2027</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I39" s="4" t="inlineStr"/>
+        <v>14095</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>10144989</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.9 мес</t>
+          <t>излишек: хватит на 17.2 мес</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
+          <t>Manyo_Complex_Ampoule</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>642</v>
+        <v>1351</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>0</v>
@@ -1821,68 +1821,66 @@
         <v>0</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>642</v>
+        <v>1351</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>17.3</v>
+        <v>15.7</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>207</v>
+        <v>331</v>
       </c>
       <c r="I40" s="4" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.3 мес</t>
+          <t>излишек: хватит на 15.7 мес</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner</t>
+          <t>Petitfee GOLD</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>4492</v>
+        <v>416</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>25008</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>44500</v>
+        <v>416</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2027</v>
+        <v>21</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17.2</v>
+        <v>15.7</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>14095</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>10144989</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.2 мес</t>
+          <t>излишек: хватит на 15.7 мес</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>352</v>
+        <v>1500</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
@@ -1891,32 +1889,32 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>352</v>
+        <v>1500</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>17.2</v>
+        <v>15.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>112</v>
+        <v>345</v>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.2 мес</t>
+          <t>излишек: хватит на 15.5 мес</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Petitfee GOLD</t>
+          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>416</v>
+        <v>187</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>0</v>
@@ -1925,32 +1923,32 @@
         <v>0</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>416</v>
+        <v>187</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.7 мес</t>
+          <t>излишек: хватит на 15.1 мес</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Manyo_Complex_Ampoule</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>1351</v>
+        <v>360</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>0</v>
@@ -1959,32 +1957,32 @@
         <v>0</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1351</v>
+        <v>360</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>331</v>
+        <v>60</v>
       </c>
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.7 мес</t>
+          <t>излишек: хватит на 14.7 мес</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>1500</v>
+        <v>117</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>0</v>
@@ -1993,32 +1991,32 @@
         <v>0</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1500</v>
+        <v>117</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>345</v>
+        <v>12</v>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.5 мес</t>
+          <t>излишек: хватит на 13.7 мес</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
+          <t>PETITFEE MASK 5</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="C46" s="4" t="n">
         <v>0</v>
@@ -2027,32 +2025,32 @@
         <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="F46" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H46" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>37</v>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.1 мес</t>
+          <t>излишек: хватит на 13.7 мес</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+          <t>Enoughcollagenwhiteningcovertip</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>360</v>
+        <v>663</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>0</v>
@@ -2061,32 +2059,32 @@
         <v>0</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>360</v>
+        <v>663</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>14.7</v>
+        <v>13.2</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 14.7 мес</t>
+          <t>излишек: хватит на 13.2 мес</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>117</v>
+        <v>648</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>0</v>
@@ -2095,32 +2093,32 @@
         <v>0</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>117</v>
+        <v>648</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>13.7</v>
+        <v>12.8</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 13.7 мес</t>
+          <t>излишек: хватит на 12.8 мес</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PETITFEE MASK 5</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>100</v>
+        <v>1490</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>0</v>
@@ -2129,32 +2127,32 @@
         <v>0</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>100</v>
+        <v>1490</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>13.7</v>
+        <v>12.5</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 13.7 мес</t>
+          <t>излишек: хватит на 12.5 мес</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>663</v>
+        <v>989</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>0</v>
@@ -2163,134 +2161,134 @@
         <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>663</v>
+        <v>989</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 13.2 мес</t>
+          <t>излишек: хватит на 12.2 мес</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.8 мес</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>COSRX_Salicylic_Acid_Cleanser</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G51" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.5 мес</t>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - CER-100  [100ml]</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.2 мес</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Black</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="G53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>запас в норме</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COSRX_Salicylic_Acid_Cleanser</t>
+          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>358</v>
+        <v>2424</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0</v>
@@ -2299,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>358</v>
+        <v>2424</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="G54" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>0</v>
@@ -2320,11 +2318,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100  [100ml]</t>
+          <t>JMSOLUTION - Mask Pack Disney</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>464</v>
+        <v>836</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0</v>
@@ -2333,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>464</v>
+        <v>836</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="G55" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
@@ -2354,11 +2352,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1030</v>
+        <v>278</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0</v>
@@ -2367,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1030</v>
+        <v>278</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
@@ -2388,11 +2386,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>2424</v>
+        <v>46</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0</v>
@@ -2401,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2424</v>
+        <v>46</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>182</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>10.3</v>
+        <v>8.5</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
@@ -2422,11 +2420,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Disney</t>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>836</v>
+        <v>6238</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0</v>
@@ -2435,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>836</v>
+        <v>6238</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>64</v>
+        <v>563</v>
       </c>
       <c r="G58" t="n">
-        <v>10.1</v>
+        <v>8.1</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
@@ -2456,11 +2454,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0</v>
@@ -2469,13 +2467,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G59" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>0</v>
@@ -2490,11 +2488,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER</t>
+          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml]</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0</v>
@@ -2503,13 +2501,13 @@
         <v>0</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>0</v>
@@ -2524,11 +2522,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
+          <t>Manyo_Galac_Vita_Serum</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>6238</v>
+        <v>753</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0</v>
@@ -2537,13 +2535,13 @@
         <v>0</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>6238</v>
+        <v>753</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>563</v>
+        <v>71</v>
       </c>
       <c r="G61" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>0</v>
@@ -2558,11 +2556,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>298</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0</v>
@@ -2571,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>298</v>
+        <v>521</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>0</v>
@@ -2592,11 +2590,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml]</t>
+          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 21</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0</v>
@@ -2605,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G63" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>0</v>
@@ -2626,11 +2624,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Manyo_Galac_Vita_Serum</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>753</v>
+        <v>3348</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0</v>
@@ -2639,13 +2637,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>753</v>
+        <v>3348</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="G64" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>0</v>
@@ -2660,11 +2658,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>521</v>
+        <v>7304</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0</v>
@@ -2673,13 +2671,13 @@
         <v>0</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>521</v>
+        <v>7304</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>49</v>
+        <v>709</v>
       </c>
       <c r="G65" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>0</v>
@@ -2694,11 +2692,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 21</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>251</v>
+        <v>50</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0</v>
@@ -2707,13 +2705,13 @@
         <v>0</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>251</v>
+        <v>50</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>0</v>
@@ -2728,11 +2726,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>3348</v>
+        <v>416</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0</v>
@@ -2741,13 +2739,13 @@
         <v>0</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>3348</v>
+        <v>416</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>325</v>
+        <v>43</v>
       </c>
       <c r="G67" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0</v>
@@ -2762,33 +2760,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>0</v>
+        <v>893</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>400</v>
+        <v>893</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="G68" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -2798,11 +2794,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>7304</v>
+        <v>922</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0</v>
@@ -2811,13 +2807,13 @@
         <v>0</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>7304</v>
+        <v>922</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>709</v>
+        <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
@@ -2832,11 +2828,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>50</v>
+        <v>3120</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0</v>
@@ -2845,13 +2841,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>50</v>
+        <v>3120</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>5</v>
+        <v>342</v>
       </c>
       <c r="G70" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>0</v>
@@ -2866,11 +2862,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0</v>
@@ -2879,13 +2875,13 @@
         <v>0</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G71" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>0</v>
@@ -2900,11 +2896,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>893</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0</v>
@@ -2913,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>893</v>
+        <v>484</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="G72" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -2934,11 +2930,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+          <t>Manyo_Ampoule_Lotion</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>922</v>
+        <v>615</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0</v>
@@ -2947,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>922</v>
+        <v>615</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G73" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
@@ -2968,33 +2964,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
+          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3004,11 +2998,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
+          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>3120</v>
+        <v>89</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0</v>
@@ -3017,13 +3011,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>3120</v>
+        <v>89</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>342</v>
+        <v>14</v>
       </c>
       <c r="G75" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>0</v>
@@ -3038,11 +3032,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>395</v>
+        <v>582</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0</v>
@@ -3051,13 +3045,13 @@
         <v>0</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>395</v>
+        <v>582</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="G76" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>0</v>
@@ -3072,11 +3066,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
+          <t>Manyo_Pure_Cleansing_Oil</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>484</v>
+        <v>194</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0</v>
@@ -3085,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>484</v>
+        <v>194</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G77" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
@@ -3106,11 +3100,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Manyo_Ampoule_Lotion</t>
+          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>615</v>
+        <v>318</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0</v>
@@ -3119,13 +3113,13 @@
         <v>0</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>615</v>
+        <v>318</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="G78" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
@@ -3140,31 +3134,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>13</v>
+        <v>793</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3174,11 +3170,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>89</v>
+        <v>931</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0</v>
@@ -3187,13 +3183,13 @@
         <v>0</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>89</v>
+        <v>931</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>14</v>
+        <v>165</v>
       </c>
       <c r="G80" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
@@ -3208,11 +3204,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>582</v>
+        <v>289</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>0</v>
@@ -3221,13 +3217,13 @@
         <v>0</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>582</v>
+        <v>289</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="G81" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>0</v>
@@ -3242,11 +3238,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Manyo_Pure_Cleansing_Oil</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>194</v>
+        <v>722</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>0</v>
@@ -3255,13 +3251,13 @@
         <v>0</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>194</v>
+        <v>722</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G82" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>0</v>
@@ -3276,33 +3272,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>793</v>
+        <v>59</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>132</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3312,11 +3306,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>0</v>
@@ -3325,13 +3319,13 @@
         <v>0</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G84" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
@@ -3346,11 +3340,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>289</v>
+        <v>51</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>0</v>
@@ -3359,13 +3353,13 @@
         <v>0</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>289</v>
+        <v>51</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="G85" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>0</v>
@@ -3380,11 +3374,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+          <t>videokamera4gneww</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>931</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>0</v>
@@ -3393,13 +3387,13 @@
         <v>0</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>931</v>
+        <v>5</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>0</v>
@@ -3414,11 +3408,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
+          <t>PETITFEE MASK 6</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>722</v>
+        <v>106</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>0</v>
@@ -3427,13 +3421,13 @@
         <v>0</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>722</v>
+        <v>106</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>0</v>
@@ -3448,31 +3442,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>59</v>
+        <v>461</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="G88" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3482,11 +3478,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
+          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>320</v>
+        <v>552</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>0</v>
@@ -3495,13 +3491,13 @@
         <v>0</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>320</v>
+        <v>552</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="G89" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>0</v>
@@ -3516,11 +3512,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PETITFEE MASK 6</t>
+          <t>Enoughcollagenwhiteningcovertip01</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>106</v>
+        <v>463</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>0</v>
@@ -3529,13 +3525,13 @@
         <v>0</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>106</v>
+        <v>463</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="G90" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
@@ -3550,11 +3546,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>videokamera4gneww</t>
+          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>345</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>0</v>
@@ -3563,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>5</v>
+        <v>345</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="G91" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>0</v>
@@ -3584,11 +3580,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
+          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>0</v>
@@ -3597,13 +3593,13 @@
         <v>0</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G92" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>0</v>
@@ -3618,33 +3614,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>461</v>
+        <v>252</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="G93" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>запас в норме</t>
@@ -3654,11 +3648,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>552</v>
+        <v>909</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>0</v>
@@ -3667,13 +3661,13 @@
         <v>0</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>552</v>
+        <v>909</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>118</v>
+        <v>269</v>
       </c>
       <c r="G94" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>0</v>
@@ -3688,11 +3682,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip01</t>
+          <t>Petitfee EGF</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>463</v>
+        <v>29</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>0</v>
@@ -3701,13 +3695,13 @@
         <v>0</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>463</v>
+        <v>29</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="G95" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>0</v>
@@ -3722,11 +3716,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>345</v>
+        <v>30</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>0</v>
@@ -3735,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>345</v>
+        <v>30</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="G96" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>0</v>
@@ -3756,11 +3750,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
+          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>0</v>
@@ -3769,13 +3763,13 @@
         <v>0</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>0</v>
@@ -3790,11 +3784,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>0</v>
@@ -3803,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G98" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>0</v>
@@ -3824,11 +3818,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>909</v>
+        <v>31</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>0</v>
@@ -3837,13 +3831,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>909</v>
+        <v>31</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>269</v>
+        <v>13</v>
       </c>
       <c r="G99" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>0</v>
@@ -3858,11 +3852,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Petitfee EGF</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>0</v>
@@ -3871,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G100" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>0</v>
@@ -3892,7 +3886,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
+          <t>JIGOTT - Collagen Healing Cream [100ml]</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -3908,10 +3902,10 @@
         <v>30</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
@@ -3926,11 +3920,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hydrogel Eye Patch</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>0</v>
@@ -3939,13 +3933,13 @@
         <v>0</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="G102" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>0</v>
@@ -3960,11 +3954,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
+          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pearl [1/2/3]*[10ea]</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>0</v>
@@ -3973,13 +3967,13 @@
         <v>0</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
@@ -3994,11 +3988,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
+          <t>EKEL Ampule Сream Сollagen [70ml]</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>0</v>
@@ -4007,13 +4001,13 @@
         <v>0</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G104" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>0</v>
@@ -4028,11 +4022,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatment [50ml]</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>0</v>
@@ -4041,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>0</v>
@@ -4062,11 +4056,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Healing Cream [100ml]</t>
+          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>0</v>
@@ -4075,13 +4069,13 @@
         <v>0</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="G106" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>0</v>
@@ -4096,11 +4090,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
+          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>146</v>
+        <v>4</v>
       </c>
       <c r="C107" s="2" t="n">
         <v>0</v>
@@ -4109,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>146</v>
+        <v>4</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="G107" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>0</v>
@@ -4130,11 +4124,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pearl [1/2/3]*[10ea]</t>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C108" s="2" t="n">
         <v>0</v>
@@ -4143,13 +4137,13 @@
         <v>0</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G108" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>0</v>
@@ -4164,11 +4158,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EKEL Ampule Сream Сollagen [70ml]</t>
+          <t>Collagen_Enough_Moisture_Foundation_21</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="C109" s="2" t="n">
         <v>0</v>
@@ -4177,13 +4171,13 @@
         <v>0</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45</v>
+        <v>260</v>
       </c>
       <c r="G109" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>0</v>
@@ -4198,11 +4192,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatment [50ml]</t>
+          <t>I'm Sorry for My Skin Крем Age Capture Vitalizer</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C110" s="2" t="n">
         <v>0</v>
@@ -4211,13 +4205,13 @@
         <v>0</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G110" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
@@ -4232,11 +4226,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
+          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml]</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="n">
         <v>0</v>
@@ -4245,13 +4239,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="G111" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
@@ -4266,11 +4260,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
+          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C112" s="2" t="n">
         <v>0</v>
@@ -4279,13 +4273,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G112" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>0</v>
@@ -4300,11 +4294,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
+          <t>Collagen_Enough_Moisture_Foundation_13</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="C113" s="2" t="n">
         <v>0</v>
@@ -4313,13 +4307,13 @@
         <v>0</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>13</v>
+        <v>332</v>
       </c>
       <c r="G113" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>0</v>
@@ -4334,11 +4328,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_21</t>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="C114" s="2" t="n">
         <v>0</v>
@@ -4347,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>260</v>
+        <v>50</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>0</v>
@@ -4368,11 +4362,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml]</t>
+          <t>Etude Baking Powder Crunch Pore Scrub треугольники 30</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C115" s="2" t="n">
         <v>0</v>
@@ -4381,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="G115" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>0</v>
@@ -4402,11 +4396,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
+          <t>Dr.Jart_Teatreatment_Toner</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C116" s="2" t="n">
         <v>0</v>
@@ -4415,13 +4409,13 @@
         <v>0</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="G116" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>0</v>
@@ -4436,11 +4430,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>I'm Sorry for My Skin Крем Age Capture Vitalizer</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C117" s="2" t="n">
         <v>0</v>
@@ -4449,13 +4443,13 @@
         <v>0</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="G117" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>0</v>
@@ -4470,11 +4464,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_13</t>
+          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 13</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>207</v>
+        <v>53</v>
       </c>
       <c r="C118" s="2" t="n">
         <v>0</v>
@@ -4483,13 +4477,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>207</v>
+        <v>53</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>332</v>
+        <v>123</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>0</v>
@@ -4504,11 +4498,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C119" s="2" t="n">
         <v>0</v>
@@ -4517,13 +4511,13 @@
         <v>0</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>0</v>
@@ -4538,11 +4532,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub треугольники 30</t>
+          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C120" s="2" t="n">
         <v>0</v>
@@ -4551,13 +4545,13 @@
         <v>0</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G120" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>0</v>
@@ -4572,11 +4566,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Dr.Jart_Teatreatment_Toner</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2" t="n">
         <v>0</v>
@@ -4585,13 +4579,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="G121" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>0</v>
@@ -4606,11 +4600,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C122" s="2" t="n">
         <v>0</v>
@@ -4619,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="G122" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>0</v>
@@ -4638,204 +4632,34 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 13</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>запас в норме</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n">
+      <c r="B123" s="6" t="n">
         <v>104629</v>
       </c>
-      <c r="C128" s="6" t="n">
-        <v>54916</v>
-      </c>
-      <c r="D128" s="6" t="n">
-        <v>17700</v>
-      </c>
-      <c r="E128" s="6" t="n">
-        <v>177245</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>10956</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="6" t="n">
-        <v>64061</v>
-      </c>
-      <c r="I128" s="6" t="n">
-        <v>19912572</v>
-      </c>
-      <c r="J128" s="5" t="inlineStr"/>
+      <c r="C123" s="6" t="n">
+        <v>51316</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>16100</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>172045</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>10895</v>
+      </c>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="6" t="n">
+        <v>59461</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>17301497</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4848,7 +4672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -5124,69 +4948,69 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule Foam [125ml]</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>979290</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Round Lab 1025 Dokdo Toner</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>990</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1245</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>760129</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Round Lab 1025 Dokdo Toner</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>990</v>
+        <v>1376</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1350</v>
+        <v>1376</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1245</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>760129</v>
-      </c>
+        <v>1121</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 36 мес</t>
@@ -5194,47 +5018,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>manyo_bifida_biome_toner</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>565812</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1439</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1439</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1094</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
+          <t>VT PDRN Essence 100</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1376</v>
+        <v>1063</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0</v>
@@ -5243,16 +5067,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1376</v>
+        <v>1063</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1121</v>
+        <v>1033</v>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
@@ -5264,11 +5088,11 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1439</v>
+        <v>1483</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0</v>
@@ -5277,32 +5101,32 @@
         <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1439</v>
+        <v>1483</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>36</v>
+        <v>32.2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1094</v>
+        <v>943</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 32.2 мес</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>VT PDRN Essence 100</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1063</v>
+        <v>1611</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0</v>
@@ -5311,100 +5135,100 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1063</v>
+        <v>1611</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1033</v>
+        <v>891</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 27.0 мес</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>264616</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>JIGOTT - MASK 15</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1445</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 28.6 мес</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>956</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="n">
-        <v>956</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>801357</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1297</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>832</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 32.8 мес</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1483</v>
+        <v>831</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0</v>
@@ -5413,32 +5237,32 @@
         <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1483</v>
+        <v>831</v>
       </c>
       <c r="F16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>32.2</v>
-      </c>
       <c r="H16" s="4" t="n">
-        <v>943</v>
+        <v>621</v>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.2 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1611</v>
+        <v>646</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0</v>
@@ -5447,66 +5271,64 @@
         <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1611</v>
+        <v>646</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>891</v>
+        <v>556</v>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 27.0 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>JIGOTT - MASK 15</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>1445</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>1445</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 28.6 мес</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g]</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>лежит без продаж</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]</t>
+          <t>Enoughcollagenwhiteningcovertip03</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1297</v>
+        <v>781</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0</v>
@@ -5515,52 +5337,54 @@
         <v>0</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1297</v>
+        <v>781</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>32.8</v>
+        <v>32.1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>832</v>
+        <v>496</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.8 мес</t>
+          <t>излишек: хватит на 32.1 мес</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
+          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>831</v>
+        <v>12</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>831</v>
+        <v>492</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>621</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr"/>
+        <v>477</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>292191</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 36 мес</t>
@@ -5568,65 +5392,65 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>646</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>646</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>556</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 36 мес</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VT Reedle Shot</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>лежит без продаж</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g]</t>
+          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>194988</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>лежит без продаж</t>
@@ -5636,11 +5460,11 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip03</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>781</v>
+        <v>428</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0</v>
@@ -5649,54 +5473,52 @@
         <v>0</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>781</v>
+        <v>428</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>32.1</v>
+        <v>36</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>496</v>
+        <v>398</v>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 32.1 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>36</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>477</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>292191</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 36 мес</t>
@@ -5704,79 +5526,81 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>VT Reedle Shot</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="2" t="n">
-        <v>452</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 15.5 мес</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>194988</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Manyo_Complex_Ampoule</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1351</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1351</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 15.7 мес</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
+          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>428</v>
+        <v>642</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
@@ -5785,32 +5609,32 @@
         <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>428</v>
+        <v>642</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>36</v>
+        <v>17.3</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>398</v>
+        <v>207</v>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 17.3 мес</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1500</v>
+        <v>403</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -5819,28 +5643,28 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1500</v>
+        <v>403</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.5</v>
+        <v>19.2</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.5 мес</t>
+          <t>излишек: хватит на 19.2 мес</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
@@ -5856,29 +5680,29 @@
         <v>420</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>36</v>
+        <v>17.9</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 17.9 мес</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Manyo_Complex_Ampoule</t>
+          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1351</v>
+        <v>375</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0</v>
@@ -5887,32 +5711,32 @@
         <v>0</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1351</v>
+        <v>375</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>15.7</v>
+        <v>19</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>331</v>
+        <v>150</v>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.7 мес</t>
+          <t>излишек: хватит на 19.0 мес</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
+          <t>ELIZAVECCA_galactomyces_Ample</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>642</v>
+        <v>137</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0</v>
@@ -5921,32 +5745,32 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>642</v>
+        <v>137</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>17.3</v>
+        <v>36</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.3 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0</v>
@@ -5955,32 +5779,32 @@
         <v>0</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>19.2</v>
+        <v>36</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="I32" s="4" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 19.2 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0</v>
@@ -5989,32 +5813,32 @@
         <v>0</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>19</v>
+        <v>17.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 19.0 мес</t>
+          <t>излишек: хватит на 17.2 мес</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
+          <t>Petitfee GOLD</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0</v>
@@ -6023,32 +5847,32 @@
         <v>0</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>17.9</v>
+        <v>15.7</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.9 мес</t>
+          <t>излишек: хватит на 15.7 мес</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+          <t>Petitfee Pink Vita Brightening Eye Mask</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0</v>
@@ -6057,32 +5881,32 @@
         <v>0</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>36</v>
+        <v>22.6</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 22.6 мес</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ELIZAVECCA_galactomyces_Ample</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>0</v>
@@ -6091,32 +5915,32 @@
         <v>0</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>36</v>
+        <v>25.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 25.8 мес</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>352</v>
+        <v>96</v>
       </c>
       <c r="C37" s="4" t="n">
         <v>0</v>
@@ -6125,32 +5949,32 @@
         <v>0</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>352</v>
+        <v>96</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>17.2</v>
+        <v>36</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 17.2 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Petitfee GOLD</t>
+          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="C38" s="4" t="n">
         <v>0</v>
@@ -6159,32 +5983,32 @@
         <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>15.7</v>
+        <v>36</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.7 мес</t>
+          <t>излишек: хватит на 36 мес</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Petitfee Pink Vita Brightening Eye Mask</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>0</v>
@@ -6193,100 +6017,98 @@
         <v>0</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>22.6</v>
+        <v>14.7</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 22.6 мес</t>
+          <t>излишек: хватит на 14.7 мес</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>159</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>159</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 25.8 мес</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>лежит без продаж</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F41" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="C41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G41" s="3" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 12.5 мес</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
+          <t>Enoughcollagenwhiteningcovertip</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>79</v>
+        <v>663</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
@@ -6295,32 +6117,32 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>79</v>
+        <v>663</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>36</v>
+        <v>13.2</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 36 мес</t>
+          <t>излишек: хватит на 13.2 мес</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+          <t>HairSet/350/8*2</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>360</v>
+        <v>107</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>0</v>
@@ -6329,66 +6151,64 @@
         <v>0</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>360</v>
+        <v>107</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>14.7</v>
+        <v>20.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 14.7 мес</t>
+          <t>излишек: хватит на 20.8 мес</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.5 мес</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>лежит без продаж</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip</t>
+          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>663</v>
+        <v>187</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>0</v>
@@ -6397,32 +6217,32 @@
         <v>0</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>663</v>
+        <v>187</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 13.2 мес</t>
+          <t>излишек: хватит на 15.1 мес</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>HairSet/350/8*2</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C46" s="4" t="n">
         <v>0</v>
@@ -6431,64 +6251,66 @@
         <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>20.8</v>
+        <v>27</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 20.8 мес</t>
+          <t>излишек: хватит на 27.0 мес</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [240ml]</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>лежит без продаж</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>излишек: хватит на 12.8 мес</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>187</v>
+        <v>989</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>0</v>
@@ -6497,32 +6319,32 @@
         <v>0</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>187</v>
+        <v>989</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>15.1</v>
+        <v>12.2</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 15.1 мес</t>
+          <t>излишек: хватит на 12.2 мес</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>0</v>
@@ -6531,32 +6353,32 @@
         <v>0</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>27</v>
+        <v>13.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>излишек: хватит на 27.0 мес</t>
+          <t>излишек: хватит на 13.7 мес</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+          <t>PETITFEE MASK 5</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>648</v>
+        <v>100</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>0</v>
@@ -6565,121 +6387,19 @@
         <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>648</v>
+        <v>100</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.8 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>989</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 12.2 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>излишек: хватит на 13.7 мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>PETITFEE MASK 5</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>излишек: хватит на 13.7 мес</t>
         </is>
